--- a/GameData/DataTables/Meta/NarrativeTable.xlsx
+++ b/GameData/DataTables/Meta/NarrativeTable.xlsx
@@ -630,8 +630,10 @@
           <t>夜雨落在旧城区的铁皮屋顶上。</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>2.5</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -661,8 +663,10 @@
           <t>我回来了。长明修理铺的灯还亮着。</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -692,8 +696,10 @@
           <t>先熟悉工作台，再一起接下邻里的维修委托。</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -738,8 +744,10 @@
           <t>reply</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -774,8 +782,10 @@
           <t>先确认红鞋和动作之间的联系，别强行抓住她。</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -820,8 +830,10 @@
           <t>response</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -856,8 +868,10 @@
           <t>让我停下来。鞋还在动，也请把它单独封存。</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -902,8 +916,10 @@
           <t>reply</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -938,8 +954,10 @@
           <t>红鞋已经封存。如果还有异常，就来长明修理铺找我。</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
   </sheetData>
